--- a/movimientos.xlsx
+++ b/movimientos.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -519,12 +519,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -555,12 +555,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -699,12 +699,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jrsera</t>
+          <t>mary</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Administrador</t>
+          <t>Marivelys Molina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
